--- a/s03/descargables/S03_ALU_04_Programa_Capacitacion.xlsx
+++ b/s03/descargables/S03_ALU_04_Programa_Capacitacion.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Constancias y evaluaciones" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selección de personal" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendario 2027" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Constancia y difusión" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Personal obligado'!$6:$6</definedName>
@@ -29,11 +30,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -121,8 +121,48 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0012224A"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="005A6472"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0012224A"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001B2430"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="008A5A12"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="008A5A12"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -154,8 +194,23 @@
         <fgColor rgb="00F2F4F8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDF3E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F4EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDECEA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -254,11 +309,70 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E4E8EE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E4E8EE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E4E8EE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E4E8EE"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E4E8EE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E4E8EE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E4E8EE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E4E8EE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E4E8EE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E4E8EE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E4E8EE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E4E8EE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -304,7 +418,7 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -316,7 +430,7 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -344,10 +458,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -375,6 +489,47 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1147,7 +1302,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L7" s="19" t="n">
+      <c r="L7" s="46" t="n">
         <v>43528</v>
       </c>
       <c r="M7" s="18">
@@ -1215,7 +1370,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L8" s="19" t="n">
+      <c r="L8" s="46" t="n">
         <v>45139</v>
       </c>
       <c r="M8" s="18">
@@ -1283,7 +1438,7 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="L9" s="19" t="n">
+      <c r="L9" s="46" t="n">
         <v>46433</v>
       </c>
       <c r="M9" s="18">
@@ -1311,7 +1466,7 @@
         <v/>
       </c>
       <c r="K10" s="21" t="n"/>
-      <c r="L10" s="23" t="n"/>
+      <c r="L10" s="47" t="n"/>
       <c r="M10" s="22">
         <f>IF($A10="","",IF(OR($F10="Sí",$K10="Sí"),"Sí","No"))</f>
         <v/>
@@ -1333,7 +1488,7 @@
         <v/>
       </c>
       <c r="K11" s="21" t="n"/>
-      <c r="L11" s="23" t="n"/>
+      <c r="L11" s="47" t="n"/>
       <c r="M11" s="22">
         <f>IF($A11="","",IF(OR($F11="Sí",$K11="Sí"),"Sí","No"))</f>
         <v/>
@@ -1355,7 +1510,7 @@
         <v/>
       </c>
       <c r="K12" s="21" t="n"/>
-      <c r="L12" s="23" t="n"/>
+      <c r="L12" s="47" t="n"/>
       <c r="M12" s="22">
         <f>IF($A12="","",IF(OR($F12="Sí",$K12="Sí"),"Sí","No"))</f>
         <v/>
@@ -1377,7 +1532,7 @@
         <v/>
       </c>
       <c r="K13" s="21" t="n"/>
-      <c r="L13" s="23" t="n"/>
+      <c r="L13" s="47" t="n"/>
       <c r="M13" s="22">
         <f>IF($A13="","",IF(OR($F13="Sí",$K13="Sí"),"Sí","No"))</f>
         <v/>
@@ -1399,7 +1554,7 @@
         <v/>
       </c>
       <c r="K14" s="21" t="n"/>
-      <c r="L14" s="23" t="n"/>
+      <c r="L14" s="47" t="n"/>
       <c r="M14" s="22">
         <f>IF($A14="","",IF(OR($F14="Sí",$K14="Sí"),"Sí","No"))</f>
         <v/>
@@ -1421,7 +1576,7 @@
         <v/>
       </c>
       <c r="K15" s="21" t="n"/>
-      <c r="L15" s="23" t="n"/>
+      <c r="L15" s="47" t="n"/>
       <c r="M15" s="22">
         <f>IF($A15="","",IF(OR($F15="Sí",$K15="Sí"),"Sí","No"))</f>
         <v/>
@@ -1443,7 +1598,7 @@
         <v/>
       </c>
       <c r="K16" s="21" t="n"/>
-      <c r="L16" s="23" t="n"/>
+      <c r="L16" s="47" t="n"/>
       <c r="M16" s="22">
         <f>IF($A16="","",IF(OR($F16="Sí",$K16="Sí"),"Sí","No"))</f>
         <v/>
@@ -1465,7 +1620,7 @@
         <v/>
       </c>
       <c r="K17" s="21" t="n"/>
-      <c r="L17" s="23" t="n"/>
+      <c r="L17" s="47" t="n"/>
       <c r="M17" s="22">
         <f>IF($A17="","",IF(OR($F17="Sí",$K17="Sí"),"Sí","No"))</f>
         <v/>
@@ -1487,7 +1642,7 @@
         <v/>
       </c>
       <c r="K18" s="21" t="n"/>
-      <c r="L18" s="23" t="n"/>
+      <c r="L18" s="47" t="n"/>
       <c r="M18" s="22">
         <f>IF($A18="","",IF(OR($F18="Sí",$K18="Sí"),"Sí","No"))</f>
         <v/>
@@ -1509,7 +1664,7 @@
         <v/>
       </c>
       <c r="K19" s="21" t="n"/>
-      <c r="L19" s="23" t="n"/>
+      <c r="L19" s="47" t="n"/>
       <c r="M19" s="22">
         <f>IF($A19="","",IF(OR($F19="Sí",$K19="Sí"),"Sí","No"))</f>
         <v/>
@@ -1531,7 +1686,7 @@
         <v/>
       </c>
       <c r="K20" s="21" t="n"/>
-      <c r="L20" s="23" t="n"/>
+      <c r="L20" s="47" t="n"/>
       <c r="M20" s="22">
         <f>IF($A20="","",IF(OR($F20="Sí",$K20="Sí"),"Sí","No"))</f>
         <v/>
@@ -1553,7 +1708,7 @@
         <v/>
       </c>
       <c r="K21" s="21" t="n"/>
-      <c r="L21" s="23" t="n"/>
+      <c r="L21" s="47" t="n"/>
       <c r="M21" s="22">
         <f>IF($A21="","",IF(OR($F21="Sí",$K21="Sí"),"Sí","No"))</f>
         <v/>
@@ -1575,7 +1730,7 @@
         <v/>
       </c>
       <c r="K22" s="21" t="n"/>
-      <c r="L22" s="23" t="n"/>
+      <c r="L22" s="47" t="n"/>
       <c r="M22" s="22">
         <f>IF($A22="","",IF(OR($F22="Sí",$K22="Sí"),"Sí","No"))</f>
         <v/>
@@ -1597,7 +1752,7 @@
         <v/>
       </c>
       <c r="K23" s="21" t="n"/>
-      <c r="L23" s="23" t="n"/>
+      <c r="L23" s="47" t="n"/>
       <c r="M23" s="22">
         <f>IF($A23="","",IF(OR($F23="Sí",$K23="Sí"),"Sí","No"))</f>
         <v/>
@@ -1619,7 +1774,7 @@
         <v/>
       </c>
       <c r="K24" s="21" t="n"/>
-      <c r="L24" s="23" t="n"/>
+      <c r="L24" s="47" t="n"/>
       <c r="M24" s="22">
         <f>IF($A24="","",IF(OR($F24="Sí",$K24="Sí"),"Sí","No"))</f>
         <v/>
@@ -1641,7 +1796,7 @@
         <v/>
       </c>
       <c r="K25" s="21" t="n"/>
-      <c r="L25" s="23" t="n"/>
+      <c r="L25" s="47" t="n"/>
       <c r="M25" s="22">
         <f>IF($A25="","",IF(OR($F25="Sí",$K25="Sí"),"Sí","No"))</f>
         <v/>
@@ -1663,7 +1818,7 @@
         <v/>
       </c>
       <c r="K26" s="21" t="n"/>
-      <c r="L26" s="23" t="n"/>
+      <c r="L26" s="47" t="n"/>
       <c r="M26" s="22">
         <f>IF($A26="","",IF(OR($F26="Sí",$K26="Sí"),"Sí","No"))</f>
         <v/>
@@ -1685,7 +1840,7 @@
         <v/>
       </c>
       <c r="K27" s="21" t="n"/>
-      <c r="L27" s="23" t="n"/>
+      <c r="L27" s="47" t="n"/>
       <c r="M27" s="22">
         <f>IF($A27="","",IF(OR($F27="Sí",$K27="Sí"),"Sí","No"))</f>
         <v/>
@@ -1707,7 +1862,7 @@
         <v/>
       </c>
       <c r="K28" s="21" t="n"/>
-      <c r="L28" s="23" t="n"/>
+      <c r="L28" s="47" t="n"/>
       <c r="M28" s="22">
         <f>IF($A28="","",IF(OR($F28="Sí",$K28="Sí"),"Sí","No"))</f>
         <v/>
@@ -1729,7 +1884,7 @@
         <v/>
       </c>
       <c r="K29" s="21" t="n"/>
-      <c r="L29" s="23" t="n"/>
+      <c r="L29" s="47" t="n"/>
       <c r="M29" s="22">
         <f>IF($A29="","",IF(OR($F29="Sí",$K29="Sí"),"Sí","No"))</f>
         <v/>
@@ -1751,7 +1906,7 @@
         <v/>
       </c>
       <c r="K30" s="21" t="n"/>
-      <c r="L30" s="23" t="n"/>
+      <c r="L30" s="47" t="n"/>
       <c r="M30" s="22">
         <f>IF($A30="","",IF(OR($F30="Sí",$K30="Sí"),"Sí","No"))</f>
         <v/>
@@ -1773,7 +1928,7 @@
         <v/>
       </c>
       <c r="K31" s="21" t="n"/>
-      <c r="L31" s="23" t="n"/>
+      <c r="L31" s="47" t="n"/>
       <c r="M31" s="22">
         <f>IF($A31="","",IF(OR($F31="Sí",$K31="Sí"),"Sí","No"))</f>
         <v/>
@@ -1795,7 +1950,7 @@
         <v/>
       </c>
       <c r="K32" s="21" t="n"/>
-      <c r="L32" s="23" t="n"/>
+      <c r="L32" s="47" t="n"/>
       <c r="M32" s="22">
         <f>IF($A32="","",IF(OR($F32="Sí",$K32="Sí"),"Sí","No"))</f>
         <v/>
@@ -1817,7 +1972,7 @@
         <v/>
       </c>
       <c r="K33" s="21" t="n"/>
-      <c r="L33" s="23" t="n"/>
+      <c r="L33" s="47" t="n"/>
       <c r="M33" s="22">
         <f>IF($A33="","",IF(OR($F33="Sí",$K33="Sí"),"Sí","No"))</f>
         <v/>
@@ -1839,7 +1994,7 @@
         <v/>
       </c>
       <c r="K34" s="21" t="n"/>
-      <c r="L34" s="23" t="n"/>
+      <c r="L34" s="47" t="n"/>
       <c r="M34" s="22">
         <f>IF($A34="","",IF(OR($F34="Sí",$K34="Sí"),"Sí","No"))</f>
         <v/>
@@ -2666,8 +2821,8 @@
       <c r="B6" s="32" t="n"/>
       <c r="C6" s="30" t="n"/>
       <c r="D6" s="30" t="n"/>
-      <c r="E6" s="33" t="n"/>
-      <c r="F6" s="34">
+      <c r="E6" s="48" t="n"/>
+      <c r="F6" s="49">
         <f>IF($E6="","",EDATE($E6,120))</f>
         <v/>
       </c>
@@ -2682,8 +2837,8 @@
       <c r="B7" s="32" t="n"/>
       <c r="C7" s="30" t="n"/>
       <c r="D7" s="30" t="n"/>
-      <c r="E7" s="33" t="n"/>
-      <c r="F7" s="34">
+      <c r="E7" s="48" t="n"/>
+      <c r="F7" s="49">
         <f>IF($E7="","",EDATE($E7,120))</f>
         <v/>
       </c>
@@ -2698,8 +2853,8 @@
       <c r="B8" s="32" t="n"/>
       <c r="C8" s="30" t="n"/>
       <c r="D8" s="30" t="n"/>
-      <c r="E8" s="33" t="n"/>
-      <c r="F8" s="34">
+      <c r="E8" s="48" t="n"/>
+      <c r="F8" s="49">
         <f>IF($E8="","",EDATE($E8,120))</f>
         <v/>
       </c>
@@ -2714,8 +2869,8 @@
       <c r="B9" s="32" t="n"/>
       <c r="C9" s="30" t="n"/>
       <c r="D9" s="30" t="n"/>
-      <c r="E9" s="33" t="n"/>
-      <c r="F9" s="34">
+      <c r="E9" s="48" t="n"/>
+      <c r="F9" s="49">
         <f>IF($E9="","",EDATE($E9,120))</f>
         <v/>
       </c>
@@ -2730,8 +2885,8 @@
       <c r="B10" s="32" t="n"/>
       <c r="C10" s="30" t="n"/>
       <c r="D10" s="30" t="n"/>
-      <c r="E10" s="33" t="n"/>
-      <c r="F10" s="34">
+      <c r="E10" s="48" t="n"/>
+      <c r="F10" s="49">
         <f>IF($E10="","",EDATE($E10,120))</f>
         <v/>
       </c>
@@ -2746,8 +2901,8 @@
       <c r="B11" s="32" t="n"/>
       <c r="C11" s="30" t="n"/>
       <c r="D11" s="30" t="n"/>
-      <c r="E11" s="33" t="n"/>
-      <c r="F11" s="34">
+      <c r="E11" s="48" t="n"/>
+      <c r="F11" s="49">
         <f>IF($E11="","",EDATE($E11,120))</f>
         <v/>
       </c>
@@ -2762,8 +2917,8 @@
       <c r="B12" s="32" t="n"/>
       <c r="C12" s="30" t="n"/>
       <c r="D12" s="30" t="n"/>
-      <c r="E12" s="33" t="n"/>
-      <c r="F12" s="34">
+      <c r="E12" s="48" t="n"/>
+      <c r="F12" s="49">
         <f>IF($E12="","",EDATE($E12,120))</f>
         <v/>
       </c>
@@ -2774,8 +2929,8 @@
       <c r="B13" s="32" t="n"/>
       <c r="C13" s="30" t="n"/>
       <c r="D13" s="30" t="n"/>
-      <c r="E13" s="33" t="n"/>
-      <c r="F13" s="34">
+      <c r="E13" s="48" t="n"/>
+      <c r="F13" s="49">
         <f>IF($E13="","",EDATE($E13,120))</f>
         <v/>
       </c>
@@ -2786,8 +2941,8 @@
       <c r="B14" s="32" t="n"/>
       <c r="C14" s="30" t="n"/>
       <c r="D14" s="30" t="n"/>
-      <c r="E14" s="33" t="n"/>
-      <c r="F14" s="34">
+      <c r="E14" s="48" t="n"/>
+      <c r="F14" s="49">
         <f>IF($E14="","",EDATE($E14,120))</f>
         <v/>
       </c>
@@ -2798,8 +2953,8 @@
       <c r="B15" s="32" t="n"/>
       <c r="C15" s="30" t="n"/>
       <c r="D15" s="30" t="n"/>
-      <c r="E15" s="33" t="n"/>
-      <c r="F15" s="34">
+      <c r="E15" s="48" t="n"/>
+      <c r="F15" s="49">
         <f>IF($E15="","",EDATE($E15,120))</f>
         <v/>
       </c>
@@ -2810,8 +2965,8 @@
       <c r="B16" s="32" t="n"/>
       <c r="C16" s="30" t="n"/>
       <c r="D16" s="30" t="n"/>
-      <c r="E16" s="33" t="n"/>
-      <c r="F16" s="34">
+      <c r="E16" s="48" t="n"/>
+      <c r="F16" s="49">
         <f>IF($E16="","",EDATE($E16,120))</f>
         <v/>
       </c>
@@ -2822,8 +2977,8 @@
       <c r="B17" s="32" t="n"/>
       <c r="C17" s="30" t="n"/>
       <c r="D17" s="30" t="n"/>
-      <c r="E17" s="33" t="n"/>
-      <c r="F17" s="34">
+      <c r="E17" s="48" t="n"/>
+      <c r="F17" s="49">
         <f>IF($E17="","",EDATE($E17,120))</f>
         <v/>
       </c>
@@ -2980,7 +3135,7 @@
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="30" t="n"/>
       <c r="B8" s="30" t="n"/>
-      <c r="C8" s="23" t="n"/>
+      <c r="C8" s="47" t="n"/>
       <c r="D8" s="21" t="n"/>
       <c r="E8" s="21" t="n"/>
       <c r="F8" s="39">
@@ -2994,7 +3149,7 @@
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="30" t="n"/>
       <c r="B9" s="30" t="n"/>
-      <c r="C9" s="23" t="n"/>
+      <c r="C9" s="47" t="n"/>
       <c r="D9" s="21" t="n"/>
       <c r="E9" s="21" t="n"/>
       <c r="F9" s="39">
@@ -3008,7 +3163,7 @@
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="30" t="n"/>
       <c r="B10" s="30" t="n"/>
-      <c r="C10" s="23" t="n"/>
+      <c r="C10" s="47" t="n"/>
       <c r="D10" s="21" t="n"/>
       <c r="E10" s="21" t="n"/>
       <c r="F10" s="39">
@@ -3022,7 +3177,7 @@
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="30" t="n"/>
       <c r="B11" s="30" t="n"/>
-      <c r="C11" s="23" t="n"/>
+      <c r="C11" s="47" t="n"/>
       <c r="D11" s="21" t="n"/>
       <c r="E11" s="21" t="n"/>
       <c r="F11" s="39">
@@ -3036,7 +3191,7 @@
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="30" t="n"/>
       <c r="B12" s="30" t="n"/>
-      <c r="C12" s="23" t="n"/>
+      <c r="C12" s="47" t="n"/>
       <c r="D12" s="21" t="n"/>
       <c r="E12" s="21" t="n"/>
       <c r="F12" s="39">
@@ -3050,7 +3205,7 @@
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="30" t="n"/>
       <c r="B13" s="30" t="n"/>
-      <c r="C13" s="23" t="n"/>
+      <c r="C13" s="47" t="n"/>
       <c r="D13" s="21" t="n"/>
       <c r="E13" s="21" t="n"/>
       <c r="F13" s="39">
@@ -3064,7 +3219,7 @@
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="30" t="n"/>
       <c r="B14" s="30" t="n"/>
-      <c r="C14" s="23" t="n"/>
+      <c r="C14" s="47" t="n"/>
       <c r="D14" s="21" t="n"/>
       <c r="E14" s="21" t="n"/>
       <c r="F14" s="39">
@@ -3078,7 +3233,7 @@
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="30" t="n"/>
       <c r="B15" s="30" t="n"/>
-      <c r="C15" s="23" t="n"/>
+      <c r="C15" s="47" t="n"/>
       <c r="D15" s="21" t="n"/>
       <c r="E15" s="21" t="n"/>
       <c r="F15" s="39">
@@ -3092,7 +3247,7 @@
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="30" t="n"/>
       <c r="B16" s="30" t="n"/>
-      <c r="C16" s="23" t="n"/>
+      <c r="C16" s="47" t="n"/>
       <c r="D16" s="21" t="n"/>
       <c r="E16" s="21" t="n"/>
       <c r="F16" s="39">
@@ -3106,7 +3261,7 @@
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="30" t="n"/>
       <c r="B17" s="30" t="n"/>
-      <c r="C17" s="23" t="n"/>
+      <c r="C17" s="47" t="n"/>
       <c r="D17" s="21" t="n"/>
       <c r="E17" s="21" t="n"/>
       <c r="F17" s="39">
@@ -3120,7 +3275,7 @@
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="30" t="n"/>
       <c r="B18" s="30" t="n"/>
-      <c r="C18" s="23" t="n"/>
+      <c r="C18" s="47" t="n"/>
       <c r="D18" s="21" t="n"/>
       <c r="E18" s="21" t="n"/>
       <c r="F18" s="39">
@@ -3134,7 +3289,7 @@
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="30" t="n"/>
       <c r="B19" s="30" t="n"/>
-      <c r="C19" s="23" t="n"/>
+      <c r="C19" s="47" t="n"/>
       <c r="D19" s="21" t="n"/>
       <c r="E19" s="21" t="n"/>
       <c r="F19" s="39">
@@ -3148,7 +3303,7 @@
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="30" t="n"/>
       <c r="B20" s="30" t="n"/>
-      <c r="C20" s="23" t="n"/>
+      <c r="C20" s="47" t="n"/>
       <c r="D20" s="21" t="n"/>
       <c r="E20" s="21" t="n"/>
       <c r="F20" s="39">
@@ -3162,7 +3317,7 @@
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="30" t="n"/>
       <c r="B21" s="30" t="n"/>
-      <c r="C21" s="23" t="n"/>
+      <c r="C21" s="47" t="n"/>
       <c r="D21" s="21" t="n"/>
       <c r="E21" s="21" t="n"/>
       <c r="F21" s="39">
@@ -3176,7 +3331,7 @@
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="30" t="n"/>
       <c r="B22" s="30" t="n"/>
-      <c r="C22" s="23" t="n"/>
+      <c r="C22" s="47" t="n"/>
       <c r="D22" s="21" t="n"/>
       <c r="E22" s="21" t="n"/>
       <c r="F22" s="39">
@@ -3190,7 +3345,7 @@
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="30" t="n"/>
       <c r="B23" s="30" t="n"/>
-      <c r="C23" s="23" t="n"/>
+      <c r="C23" s="47" t="n"/>
       <c r="D23" s="21" t="n"/>
       <c r="E23" s="21" t="n"/>
       <c r="F23" s="39">
@@ -3204,7 +3359,7 @@
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="30" t="n"/>
       <c r="B24" s="30" t="n"/>
-      <c r="C24" s="23" t="n"/>
+      <c r="C24" s="47" t="n"/>
       <c r="D24" s="21" t="n"/>
       <c r="E24" s="21" t="n"/>
       <c r="F24" s="39">
@@ -3218,7 +3373,7 @@
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="30" t="n"/>
       <c r="B25" s="30" t="n"/>
-      <c r="C25" s="23" t="n"/>
+      <c r="C25" s="47" t="n"/>
       <c r="D25" s="21" t="n"/>
       <c r="E25" s="21" t="n"/>
       <c r="F25" s="39">
@@ -3232,7 +3387,7 @@
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="30" t="n"/>
       <c r="B26" s="30" t="n"/>
-      <c r="C26" s="23" t="n"/>
+      <c r="C26" s="47" t="n"/>
       <c r="D26" s="21" t="n"/>
       <c r="E26" s="21" t="n"/>
       <c r="F26" s="39">
@@ -3246,7 +3401,7 @@
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="30" t="n"/>
       <c r="B27" s="30" t="n"/>
-      <c r="C27" s="23" t="n"/>
+      <c r="C27" s="47" t="n"/>
       <c r="D27" s="21" t="n"/>
       <c r="E27" s="21" t="n"/>
       <c r="F27" s="39">
@@ -3260,7 +3415,7 @@
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="30" t="n"/>
       <c r="B28" s="30" t="n"/>
-      <c r="C28" s="23" t="n"/>
+      <c r="C28" s="47" t="n"/>
       <c r="D28" s="21" t="n"/>
       <c r="E28" s="21" t="n"/>
       <c r="F28" s="39">
@@ -3274,7 +3429,7 @@
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="30" t="n"/>
       <c r="B29" s="30" t="n"/>
-      <c r="C29" s="23" t="n"/>
+      <c r="C29" s="47" t="n"/>
       <c r="D29" s="21" t="n"/>
       <c r="E29" s="21" t="n"/>
       <c r="F29" s="39">
@@ -3288,7 +3443,7 @@
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="30" t="n"/>
       <c r="B30" s="30" t="n"/>
-      <c r="C30" s="23" t="n"/>
+      <c r="C30" s="47" t="n"/>
       <c r="D30" s="21" t="n"/>
       <c r="E30" s="21" t="n"/>
       <c r="F30" s="39">
@@ -3302,7 +3457,7 @@
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="30" t="n"/>
       <c r="B31" s="30" t="n"/>
-      <c r="C31" s="23" t="n"/>
+      <c r="C31" s="47" t="n"/>
       <c r="D31" s="21" t="n"/>
       <c r="E31" s="21" t="n"/>
       <c r="F31" s="39">
@@ -3316,7 +3471,7 @@
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="30" t="n"/>
       <c r="B32" s="30" t="n"/>
-      <c r="C32" s="23" t="n"/>
+      <c r="C32" s="47" t="n"/>
       <c r="D32" s="21" t="n"/>
       <c r="E32" s="21" t="n"/>
       <c r="F32" s="39">
@@ -3330,7 +3485,7 @@
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="30" t="n"/>
       <c r="B33" s="30" t="n"/>
-      <c r="C33" s="23" t="n"/>
+      <c r="C33" s="47" t="n"/>
       <c r="D33" s="21" t="n"/>
       <c r="E33" s="21" t="n"/>
       <c r="F33" s="39">
@@ -3344,7 +3499,7 @@
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="30" t="n"/>
       <c r="B34" s="30" t="n"/>
-      <c r="C34" s="23" t="n"/>
+      <c r="C34" s="47" t="n"/>
       <c r="D34" s="21" t="n"/>
       <c r="E34" s="21" t="n"/>
       <c r="F34" s="39">
@@ -3358,7 +3513,7 @@
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="30" t="n"/>
       <c r="B35" s="30" t="n"/>
-      <c r="C35" s="23" t="n"/>
+      <c r="C35" s="47" t="n"/>
       <c r="D35" s="21" t="n"/>
       <c r="E35" s="21" t="n"/>
       <c r="F35" s="39">
@@ -3372,7 +3527,7 @@
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="30" t="n"/>
       <c r="B36" s="30" t="n"/>
-      <c r="C36" s="23" t="n"/>
+      <c r="C36" s="47" t="n"/>
       <c r="D36" s="21" t="n"/>
       <c r="E36" s="21" t="n"/>
       <c r="F36" s="39">
@@ -3386,7 +3541,7 @@
     <row r="37" ht="28" customHeight="1">
       <c r="A37" s="30" t="n"/>
       <c r="B37" s="30" t="n"/>
-      <c r="C37" s="23" t="n"/>
+      <c r="C37" s="47" t="n"/>
       <c r="D37" s="21" t="n"/>
       <c r="E37" s="21" t="n"/>
       <c r="F37" s="39">
@@ -3649,7 +3804,7 @@
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="30" t="n"/>
-      <c r="B19" s="23" t="n"/>
+      <c r="B19" s="47" t="n"/>
       <c r="C19" s="30" t="n"/>
       <c r="D19" s="30" t="n"/>
       <c r="E19" s="21" t="n"/>
@@ -3657,7 +3812,7 @@
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="30" t="n"/>
-      <c r="B20" s="23" t="n"/>
+      <c r="B20" s="47" t="n"/>
       <c r="C20" s="30" t="n"/>
       <c r="D20" s="30" t="n"/>
       <c r="E20" s="21" t="n"/>
@@ -3665,7 +3820,7 @@
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="30" t="n"/>
-      <c r="B21" s="23" t="n"/>
+      <c r="B21" s="47" t="n"/>
       <c r="C21" s="30" t="n"/>
       <c r="D21" s="30" t="n"/>
       <c r="E21" s="21" t="n"/>
@@ -3673,7 +3828,7 @@
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="30" t="n"/>
-      <c r="B22" s="23" t="n"/>
+      <c r="B22" s="47" t="n"/>
       <c r="C22" s="30" t="n"/>
       <c r="D22" s="30" t="n"/>
       <c r="E22" s="21" t="n"/>
@@ -3681,7 +3836,7 @@
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="30" t="n"/>
-      <c r="B23" s="23" t="n"/>
+      <c r="B23" s="47" t="n"/>
       <c r="C23" s="30" t="n"/>
       <c r="D23" s="30" t="n"/>
       <c r="E23" s="21" t="n"/>
@@ -3689,7 +3844,7 @@
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="30" t="n"/>
-      <c r="B24" s="23" t="n"/>
+      <c r="B24" s="47" t="n"/>
       <c r="C24" s="30" t="n"/>
       <c r="D24" s="30" t="n"/>
       <c r="E24" s="21" t="n"/>
@@ -3697,7 +3852,7 @@
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="30" t="n"/>
-      <c r="B25" s="23" t="n"/>
+      <c r="B25" s="47" t="n"/>
       <c r="C25" s="30" t="n"/>
       <c r="D25" s="30" t="n"/>
       <c r="E25" s="21" t="n"/>
@@ -3705,7 +3860,7 @@
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="30" t="n"/>
-      <c r="B26" s="23" t="n"/>
+      <c r="B26" s="47" t="n"/>
       <c r="C26" s="30" t="n"/>
       <c r="D26" s="30" t="n"/>
       <c r="E26" s="21" t="n"/>
@@ -3713,7 +3868,7 @@
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="30" t="n"/>
-      <c r="B27" s="23" t="n"/>
+      <c r="B27" s="47" t="n"/>
       <c r="C27" s="30" t="n"/>
       <c r="D27" s="30" t="n"/>
       <c r="E27" s="21" t="n"/>
@@ -3721,7 +3876,7 @@
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="30" t="n"/>
-      <c r="B28" s="23" t="n"/>
+      <c r="B28" s="47" t="n"/>
       <c r="C28" s="30" t="n"/>
       <c r="D28" s="30" t="n"/>
       <c r="E28" s="21" t="n"/>
@@ -3729,7 +3884,7 @@
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="30" t="n"/>
-      <c r="B29" s="23" t="n"/>
+      <c r="B29" s="47" t="n"/>
       <c r="C29" s="30" t="n"/>
       <c r="D29" s="30" t="n"/>
       <c r="E29" s="21" t="n"/>
@@ -3737,7 +3892,7 @@
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="30" t="n"/>
-      <c r="B30" s="23" t="n"/>
+      <c r="B30" s="47" t="n"/>
       <c r="C30" s="30" t="n"/>
       <c r="D30" s="30" t="n"/>
       <c r="E30" s="21" t="n"/>
@@ -3745,7 +3900,7 @@
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="30" t="n"/>
-      <c r="B31" s="23" t="n"/>
+      <c r="B31" s="47" t="n"/>
       <c r="C31" s="30" t="n"/>
       <c r="D31" s="30" t="n"/>
       <c r="E31" s="21" t="n"/>
@@ -3753,7 +3908,7 @@
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="30" t="n"/>
-      <c r="B32" s="23" t="n"/>
+      <c r="B32" s="47" t="n"/>
       <c r="C32" s="30" t="n"/>
       <c r="D32" s="30" t="n"/>
       <c r="E32" s="21" t="n"/>
@@ -3761,7 +3916,7 @@
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="30" t="n"/>
-      <c r="B33" s="23" t="n"/>
+      <c r="B33" s="47" t="n"/>
       <c r="C33" s="30" t="n"/>
       <c r="D33" s="30" t="n"/>
       <c r="E33" s="21" t="n"/>
@@ -3769,7 +3924,7 @@
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="30" t="n"/>
-      <c r="B34" s="23" t="n"/>
+      <c r="B34" s="47" t="n"/>
       <c r="C34" s="30" t="n"/>
       <c r="D34" s="30" t="n"/>
       <c r="E34" s="21" t="n"/>
@@ -3777,7 +3932,7 @@
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="30" t="n"/>
-      <c r="B35" s="23" t="n"/>
+      <c r="B35" s="47" t="n"/>
       <c r="C35" s="30" t="n"/>
       <c r="D35" s="30" t="n"/>
       <c r="E35" s="21" t="n"/>
@@ -3785,7 +3940,7 @@
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="30" t="n"/>
-      <c r="B36" s="23" t="n"/>
+      <c r="B36" s="47" t="n"/>
       <c r="C36" s="30" t="n"/>
       <c r="D36" s="30" t="n"/>
       <c r="E36" s="21" t="n"/>
@@ -3793,7 +3948,7 @@
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="A37" s="30" t="n"/>
-      <c r="B37" s="23" t="n"/>
+      <c r="B37" s="47" t="n"/>
       <c r="C37" s="30" t="n"/>
       <c r="D37" s="30" t="n"/>
       <c r="E37" s="21" t="n"/>
@@ -3801,7 +3956,7 @@
     </row>
     <row r="38" ht="28" customHeight="1">
       <c r="A38" s="30" t="n"/>
-      <c r="B38" s="23" t="n"/>
+      <c r="B38" s="47" t="n"/>
       <c r="C38" s="30" t="n"/>
       <c r="D38" s="30" t="n"/>
       <c r="E38" s="21" t="n"/>
@@ -4177,4 +4332,637 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:F58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2">
+      <c r="B2" s="50" t="inlineStr">
+        <is>
+          <t>8 · CONSTANCIA, DIFUSIÓN Y HORAS DE REFERENCIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="51" t="inlineStr">
+        <is>
+          <t>Lo que la norma exige, y lo que se toma prestado de la guía de la CNBV señalándolo como tal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6">
+      <c r="B6" s="52" t="inlineStr">
+        <is>
+          <t>A · Qué debe contener la constancia</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="51" t="inlineStr">
+        <is>
+          <t>RCG 39 Bis 1 exige expedirla y exige evaluación previa, pero NO dice qué debe decir. Estos ocho puntos vienen de la guía de la CNBV para el régimen financiero; se adoptan como buena práctica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9" ht="26" customHeight="1">
+      <c r="B9" s="53" t="inlineStr">
+        <is>
+          <t>Elemento</t>
+        </is>
+      </c>
+      <c r="C9" s="53" t="inlineStr">
+        <is>
+          <t>Por qué</t>
+        </is>
+      </c>
+      <c r="D9" s="53" t="inlineStr">
+        <is>
+          <t>¿Lo trae la nuestra?</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="B10" s="54" t="inlineStr">
+        <is>
+          <t>Nombre completo del personal capacitado, sin abreviaturas</t>
+        </is>
+      </c>
+      <c r="C10" s="54" t="inlineStr">
+        <is>
+          <t>Es la persona cuya capacitación se está acreditando.</t>
+        </is>
+      </c>
+      <c r="D10" s="54" t="inlineStr"/>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="B11" s="54" t="inlineStr">
+        <is>
+          <t>Cargo del personal capacitado</t>
+        </is>
+      </c>
+      <c r="C11" s="54" t="inlineStr">
+        <is>
+          <t>Permite cotejar contra la hoja «Personal obligado» y contra el temario dirigido a ese cargo.</t>
+        </is>
+      </c>
+      <c r="D11" s="54" t="inlineStr"/>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="B12" s="54" t="inlineStr">
+        <is>
+          <t>Nombre, denominación o razón social de quien impartió</t>
+        </is>
+      </c>
+      <c r="C12" s="54" t="inlineStr">
+        <is>
+          <t>Sin esto no se puede verificar la experiencia de quien capacitó.</t>
+        </is>
+      </c>
+      <c r="D12" s="54" t="inlineStr"/>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="B13" s="54" t="inlineStr">
+        <is>
+          <t>Fecha o periodo en que se llevó a cabo</t>
+        </is>
+      </c>
+      <c r="C13" s="54" t="inlineStr">
+        <is>
+          <t>Es lo que acredita que cayó dentro del periodo anual.</t>
+        </is>
+      </c>
+      <c r="D13" s="54" t="inlineStr"/>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="B14" s="54" t="inlineStr">
+        <is>
+          <t>Horas totales de duración</t>
+        </is>
+      </c>
+      <c r="C14" s="54" t="inlineStr">
+        <is>
+          <t>La norma de Actividades Vulnerables no fija horas, pero la constancia sí debe decir cuántas fueron.</t>
+        </is>
+      </c>
+      <c r="D14" s="54" t="inlineStr"/>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="B15" s="54" t="inlineStr">
+        <is>
+          <t>Resultado de la evaluación sobre los conocimientos adquiridos</t>
+        </is>
+      </c>
+      <c r="C15" s="54" t="inlineStr">
+        <is>
+          <t>RCG 39 Bis 1: sin evaluación previa no se puede expedir la constancia.</t>
+        </is>
+      </c>
+      <c r="D15" s="54" t="inlineStr"/>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="B16" s="54" t="inlineStr">
+        <is>
+          <t>Tipo de capacitación: presencial, en línea o mixta</t>
+        </is>
+      </c>
+      <c r="C16" s="54" t="inlineStr">
+        <is>
+          <t>Debe coincidir con la modalidad declarada en el programa anual.</t>
+        </is>
+      </c>
+      <c r="D16" s="54" t="inlineStr"/>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="B17" s="54" t="inlineStr">
+        <is>
+          <t>Nombre, firma y cargo de quien impartió, y cómo acredita sus CINCO años</t>
+        </is>
+      </c>
+      <c r="C17" s="54" t="inlineStr">
+        <is>
+          <t>RCG 39 Bis fr. III. Aquí NO va «certificado de la Comisión»: eso es del régimen financiero.</t>
+        </is>
+      </c>
+      <c r="D17" s="54" t="inlineStr"/>
+    </row>
+    <row r="18"/>
+    <row r="19" ht="40" customHeight="1">
+      <c r="B19" s="55" t="inlineStr">
+        <is>
+          <t>OJO · La guía de la CNBV pide en este punto el número de certificado vigente emitido por la Comisión. Eso NO aplica a Actividades Vulnerables: aquí lo que se acredita son los cinco años de experiencia del artículo 39 Bis, fracción III.</t>
+        </is>
+      </c>
+      <c r="C19" s="58" t="n"/>
+      <c r="D19" s="59" t="n"/>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="B21" s="52" t="inlineStr">
+        <is>
+          <t>B · Difusión — la mitad olvidada del artículo</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="51" t="inlineStr">
+        <is>
+          <t>El RCG 39 Bis dice, textual, «programas de capacitación Y DIFUSIÓN». La difusión es obligación, no adorno, y casi ningún programa la documenta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24" ht="26" customHeight="1">
+      <c r="B24" s="53" t="inlineStr">
+        <is>
+          <t>Canal o medio</t>
+        </is>
+      </c>
+      <c r="C24" s="53" t="inlineStr">
+        <is>
+          <t>Qué se difunde por ahí</t>
+        </is>
+      </c>
+      <c r="D24" s="53" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E24" s="53" t="inlineStr">
+        <is>
+          <t>Frecuencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="B25" s="54" t="inlineStr">
+        <is>
+          <t>Correo electrónico interno</t>
+        </is>
+      </c>
+      <c r="C25" s="54" t="inlineStr">
+        <is>
+          <t>Reformas a la Ley, al Reglamento y a las Reglas, en cuanto se publican en el DOF</t>
+        </is>
+      </c>
+      <c r="D25" s="54" t="inlineStr">
+        <is>
+          <t>[cargo]</t>
+        </is>
+      </c>
+      <c r="E25" s="54" t="inlineStr">
+        <is>
+          <t>Al publicarse</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1">
+      <c r="B26" s="54" t="inlineStr">
+        <is>
+          <t>Boletín o comunicado periódico</t>
+        </is>
+      </c>
+      <c r="C26" s="54" t="inlineStr">
+        <is>
+          <t>Técnicas, métodos y tendencias para prevenir y detectar operaciones del 400 Bis y delitos relacionados (fr. II)</t>
+        </is>
+      </c>
+      <c r="D26" s="54" t="inlineStr">
+        <is>
+          <t>[cargo]</t>
+        </is>
+      </c>
+      <c r="E26" s="54" t="inlineStr">
+        <is>
+          <t>[trimestral]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="B27" s="54" t="inlineStr">
+        <is>
+          <t>Intranet o carpeta compartida</t>
+        </is>
+      </c>
+      <c r="C27" s="54" t="inlineStr">
+        <is>
+          <t>Versión vigente del Manual de Políticas Internas y sus documentos por referencia</t>
+        </is>
+      </c>
+      <c r="D27" s="54" t="inlineStr">
+        <is>
+          <t>[cargo]</t>
+        </is>
+      </c>
+      <c r="E27" s="54" t="inlineStr">
+        <is>
+          <t>Al actualizarse</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="B28" s="54" t="inlineStr">
+        <is>
+          <t>Reunión de área</t>
+        </is>
+      </c>
+      <c r="C28" s="54" t="inlineStr">
+        <is>
+          <t>Resultados de la evaluación de Riesgos y qué cambió para cada área</t>
+        </is>
+      </c>
+      <c r="D28" s="54" t="inlineStr">
+        <is>
+          <t>[cargo]</t>
+        </is>
+      </c>
+      <c r="E28" s="54" t="inlineStr">
+        <is>
+          <t>[anual]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="B29" s="54" t="inlineStr">
+        <is>
+          <t>[otro canal propio]</t>
+        </is>
+      </c>
+      <c r="C29" s="54" t="inlineStr"/>
+      <c r="D29" s="54" t="inlineStr">
+        <is>
+          <t>[cargo]</t>
+        </is>
+      </c>
+      <c r="E29" s="54" t="inlineStr"/>
+    </row>
+    <row r="30"/>
+    <row r="31" ht="40" customHeight="1">
+      <c r="B31" s="55" t="inlineStr">
+        <is>
+          <t>La evidencia de la difusión se conserva DIEZ años, igual que la de la capacitación: el artículo 39 Bis 1 cubre «los programas, talleres, materiales, listas de asistencia, evaluaciones, constancias y cualquier otro documento». Guarde el correo enviado, no sólo el archivo adjunto.</t>
+        </is>
+      </c>
+      <c r="C31" s="58" t="n"/>
+      <c r="D31" s="59" t="n"/>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="B33" s="52" t="inlineStr">
+        <is>
+          <t>C · Horas por cargo — referencia externa, no obligación</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="51" t="inlineStr">
+        <is>
+          <t>La norma de Actividades Vulnerables NO fija horas mínimas. La única referencia publicada en México es la guía de la CNBV para el régimen financiero. Se incluye como punto de partida, y así debe citarse si alguien pregunta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36" ht="26" customHeight="1">
+      <c r="B36" s="53" t="inlineStr">
+        <is>
+          <t>Cargo o función</t>
+        </is>
+      </c>
+      <c r="C36" s="53" t="inlineStr">
+        <is>
+          <t>Horas anuales sugeridas por la CNBV</t>
+        </is>
+      </c>
+      <c r="D36" s="53" t="inlineStr">
+        <is>
+          <t>Equivalente en Actividad Vulnerable</t>
+        </is>
+      </c>
+      <c r="E36" s="53" t="inlineStr">
+        <is>
+          <t>Nuestras horas</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="B37" s="54" t="inlineStr">
+        <is>
+          <t>Consejo de administración</t>
+        </is>
+      </c>
+      <c r="C37" s="54" t="inlineStr">
+        <is>
+          <t>20 h</t>
+        </is>
+      </c>
+      <c r="D37" s="54" t="inlineStr">
+        <is>
+          <t>Consejo de administración o administrador único</t>
+        </is>
+      </c>
+      <c r="E37" s="54" t="inlineStr"/>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="B38" s="54" t="inlineStr">
+        <is>
+          <t>Alta dirección</t>
+        </is>
+      </c>
+      <c r="C38" s="54" t="inlineStr">
+        <is>
+          <t>20 h</t>
+        </is>
+      </c>
+      <c r="D38" s="54" t="inlineStr">
+        <is>
+          <t>Directivos y funcionarios</t>
+        </is>
+      </c>
+      <c r="E38" s="54" t="inlineStr"/>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="B39" s="54" t="inlineStr">
+        <is>
+          <t>Personal de primer contacto con el Cliente</t>
+        </is>
+      </c>
+      <c r="C39" s="54" t="inlineStr">
+        <is>
+          <t>30 h</t>
+        </is>
+      </c>
+      <c r="D39" s="54" t="inlineStr">
+        <is>
+          <t>Quien participa en la identificación o conocimiento del Cliente, o en el envío de Avisos</t>
+        </is>
+      </c>
+      <c r="E39" s="54" t="inlineStr"/>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="B40" s="54" t="inlineStr">
+        <is>
+          <t>Auditor interno</t>
+        </is>
+      </c>
+      <c r="C40" s="54" t="inlineStr">
+        <is>
+          <t>30 h</t>
+        </is>
+      </c>
+      <c r="D40" s="54" t="inlineStr">
+        <is>
+          <t>Quien realiza actividades de auditoría</t>
+        </is>
+      </c>
+      <c r="E40" s="54" t="inlineStr"/>
+    </row>
+    <row r="41" ht="34" customHeight="1">
+      <c r="B41" s="54" t="inlineStr">
+        <is>
+          <t>Oficial de Cumplimiento o Representante y Comité</t>
+        </is>
+      </c>
+      <c r="C41" s="54" t="inlineStr">
+        <is>
+          <t>40 h</t>
+        </is>
+      </c>
+      <c r="D41" s="54" t="inlineStr">
+        <is>
+          <t>Persona Representante Encargada de Cumplimiento — aquí NO hay Comité</t>
+        </is>
+      </c>
+      <c r="E41" s="54" t="inlineStr"/>
+    </row>
+    <row r="42"/>
+    <row r="43" ht="40" customHeight="1">
+      <c r="B43" s="56" t="inlineStr">
+        <is>
+          <t>Ese cuadro es del régimen financiero: artículo 115 de la Ley de Instituciones de Crédito y Disposiciones de la CNBV. No es exigible a quien realiza una Actividad Vulnerable. Sirve para no partir de cero y para sostener por qué se eligieron las horas que se eligieron.</t>
+        </is>
+      </c>
+      <c r="C43" s="58" t="n"/>
+      <c r="D43" s="59" t="n"/>
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="B45" s="60" t="inlineStr">
+        <is>
+          <t>D · Diez años. Siempre.</t>
+        </is>
+      </c>
+      <c r="C45" s="61" t="n"/>
+      <c r="D45" s="61" t="n"/>
+      <c r="E45" s="61" t="n"/>
+      <c r="F45" s="61" t="n"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="62" t="inlineStr">
+        <is>
+          <t>Toda la evidencia de capacitación y difusión se conserva DIEZ años. No hay plazo menor en ninguna hipótesis.</t>
+        </is>
+      </c>
+      <c r="C46" s="61" t="n"/>
+      <c r="D46" s="61" t="n"/>
+      <c r="E46" s="61" t="n"/>
+      <c r="F46" s="61" t="n"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="61" t="n"/>
+      <c r="C47" s="61" t="n"/>
+      <c r="D47" s="61" t="n"/>
+      <c r="E47" s="61" t="n"/>
+      <c r="F47" s="61" t="n"/>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="B48" s="53" t="inlineStr">
+        <is>
+          <t>Qué se conserva</t>
+        </is>
+      </c>
+      <c r="C48" s="53" t="inlineStr">
+        <is>
+          <t>Cuánto</t>
+        </is>
+      </c>
+      <c r="D48" s="53" t="inlineStr">
+        <is>
+          <t>Desde cuándo · fundamento</t>
+        </is>
+      </c>
+      <c r="E48" s="61" t="n"/>
+      <c r="F48" s="61" t="n"/>
+    </row>
+    <row r="49" ht="40" customHeight="1">
+      <c r="B49" s="63" t="inlineStr">
+        <is>
+          <t>Programas, talleres, materiales, listas de asistencia, evaluaciones, constancias y cualquier otro documento que compruebe que la capacitación se llevó a cabo</t>
+        </is>
+      </c>
+      <c r="C49" s="63" t="inlineStr">
+        <is>
+          <t>DIEZ años</t>
+        </is>
+      </c>
+      <c r="D49" s="63" t="inlineStr">
+        <is>
+          <t>Desde cada evento de capacitación · RCG 39 Bis 1</t>
+        </is>
+      </c>
+      <c r="E49" s="61" t="n"/>
+      <c r="F49" s="61" t="n"/>
+    </row>
+    <row r="50" ht="40" customHeight="1">
+      <c r="B50" s="63" t="inlineStr">
+        <is>
+          <t>La evidencia de la difusión: el correo enviado, el boletín, el acuse de publicación en intranet</t>
+        </is>
+      </c>
+      <c r="C50" s="63" t="inlineStr">
+        <is>
+          <t>DIEZ años</t>
+        </is>
+      </c>
+      <c r="D50" s="63" t="inlineStr">
+        <is>
+          <t>Mismo artículo: cubre «cualquier otro documento» · RCG 39 Bis 1</t>
+        </is>
+      </c>
+      <c r="E50" s="61" t="n"/>
+      <c r="F50" s="61" t="n"/>
+    </row>
+    <row r="52" ht="58" customHeight="1">
+      <c r="B52" s="64" t="inlineStr">
+        <is>
+          <t>SI ALGUIEN LLEGA CON UN CINCO, viene de uno de dos lugares y ninguno aplica hoy. Uno: del texto del artículo 18, fracción IV de la Ley ANTERIOR a la reforma del 16 de julio de 2025, que sí fijaba cinco años; la reforma lo subió a diez. Dos: de la guía de capacitación de la CNBV, que es del régimen financiero. En Actividades Vulnerables, después de la reforma, son diez en todos los casos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="52" t="inlineStr">
+        <is>
+          <t>E · Lo demás que no se copia del régimen financiero</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="26" customHeight="1">
+      <c r="B56" s="53" t="inlineStr">
+        <is>
+          <t>Tema</t>
+        </is>
+      </c>
+      <c r="C56" s="53" t="inlineStr">
+        <is>
+          <t>Régimen financiero (CNBV)</t>
+        </is>
+      </c>
+      <c r="D56" s="53" t="inlineStr">
+        <is>
+          <t>Actividad Vulnerable (LFPIORPI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="40" customHeight="1">
+      <c r="B57" s="54" t="inlineStr">
+        <is>
+          <t>Quien imparte la capacitación</t>
+        </is>
+      </c>
+      <c r="C57" s="54" t="inlineStr">
+        <is>
+          <t>Certificación ante la Comisión, sólo deseable</t>
+        </is>
+      </c>
+      <c r="D57" s="54" t="inlineStr">
+        <is>
+          <t>CINCO años de experiencia, acreditados y obligatorios · RCG 39 Bis fr. III</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="40" customHeight="1">
+      <c r="B58" s="54" t="inlineStr">
+        <is>
+          <t>Quién coordina el cumplimiento</t>
+        </is>
+      </c>
+      <c r="C58" s="54" t="inlineStr">
+        <is>
+          <t>Oficial de Cumplimiento y Comité de Comunicación y Control</t>
+        </is>
+      </c>
+      <c r="D58" s="54" t="inlineStr">
+        <is>
+          <t>Persona Representante Encargada de Cumplimiento. El Comité NO existe aquí</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B43:D43"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>